--- a/audit-template-builder/frontend/templates/invoice_workbook.xlsx
+++ b/audit-template-builder/frontend/templates/invoice_workbook.xlsx
@@ -373,7 +373,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Questions? Contact EES-WI  |  ira@ees-wi.org |  608-460-7419</t>
+    <t>ira@ees-wi.org  |  608-460-7419</t>
   </si>
   <si>
     <t>ENERGY EFFICIENCY SERVICES of WISCONSIN</t>
